--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49757-2022 artfynd.xlsx
+++ b/artfynd/A 49757-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131734802</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>131734804</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>131738028</v>
       </c>
       <c r="B4" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>131734803</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
